--- a/nablarch_sample_aws/アプリケーション方式設計書_7処理方式共通_7.11暗号化・ハッシュ化_AWS.xlsx
+++ b/nablarch_sample_aws/アプリケーション方式設計書_7処理方式共通_7.11暗号化・ハッシュ化_AWS.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="26130"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{213CE024-B820-45BE-8B7A-E127E8C9FBA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F50205A-F5A1-4C2E-A904-C6101B530018}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1245" yWindow="-120" windowWidth="27675" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -558,9 +558,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>ファイルを復号するためのマネージドワークフローの設定 | AWS Transfer Family ユーザーガイド</t>
-  </si>
-  <si>
     <t>Transfer Familyがサポートするのは受信時の復号のみなので、送信時の暗号化はLambdaによって実装する。</t>
     <rPh sb="24" eb="27">
       <t>ジュシンジ</t>
@@ -580,9 +577,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>Bouncy Castle for Java Documentation</t>
-  </si>
-  <si>
     <t>暗号化にはBouncy Castleを使用する。</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -593,6 +587,12 @@
   <si>
     <t>利用して実施する。</t>
     <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>https://docs.aws.amazon.com/ja_jp/transfer/latest/userguide/workflow-decrypt-tutorial.html</t>
+  </si>
+  <si>
+    <t>https://www.bouncycastle.org/documentation/documentation-java/</t>
   </si>
 </sst>
 </file>
@@ -1882,12 +1882,12 @@
     </row>
     <row r="41" spans="4:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F41" s="26" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="42" spans="4:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F42" s="26" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="43" spans="4:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
@@ -1910,22 +1910,22 @@
     </row>
     <row r="47" spans="4:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F47" s="27" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
     </row>
     <row r="49" spans="6:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F49" s="17" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="50" spans="6:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F50" s="17" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="52" spans="6:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="F52" s="27" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
     </row>
   </sheetData>
